--- a/DEAP_AROUSAL_Final_Results1.30 (2).xlsx
+++ b/DEAP_AROUSAL_Final_Results1.30 (2).xlsx
@@ -1,37 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mycode\EEG_C2PCI-NET\new_trail\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A73D68A-C8D6-4A27-B47B-055EF4998A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="18864" windowHeight="10656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>Subject ID</t>
+  </si>
+  <si>
+    <t>Best Accuracy</t>
+  </si>
+  <si>
+    <t>Best F1 Score</t>
+  </si>
+  <si>
+    <t>64.53    46.85</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9,92</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +91,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,384 +416,388 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Subject ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Best Accuracy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Best F1 Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>60</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.5659722222222222</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C2">
+        <v>0.56597222222222221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>60.16666666666667</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.3979823592878223</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B3">
+        <v>60.166666666666671</v>
+      </c>
+      <c r="C3">
+        <v>0.39798235928782227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>74.83333333333333</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.4526308157975821</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B4">
+        <v>74.833333333333329</v>
+      </c>
+      <c r="C4">
+        <v>0.45263081579758208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>48.66666666666667</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.4866153281994866</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B5">
+        <v>48.666666666666671</v>
+      </c>
+      <c r="C5">
+        <v>0.48661532819948661</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>54</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.3866666666666667</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="C6">
+        <v>0.38666666666666671</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.3778699451933047</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B7">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="C7">
+        <v>0.37786994519330469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>64.33333333333333</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5527690700104493</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B8">
+        <v>64.333333333333329</v>
+      </c>
+      <c r="C8">
+        <v>0.55276907001044928</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
-        <v>57.49999999999999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.3650793650793651</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B9">
+        <v>57.499999999999993</v>
+      </c>
+      <c r="C9">
+        <v>0.36507936507936511</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
-        <v>61.83333333333333</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.4756345623227786</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B10">
+        <v>61.833333333333329</v>
+      </c>
+      <c r="C10">
+        <v>0.47563456232277862</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
-        <v>59.33333333333334</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11">
+        <v>59.333333333333343</v>
+      </c>
+      <c r="C11">
         <v>0.4993160054719562</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
-        <v>58.66666666666666</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.436150056839712</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="B12">
+        <v>58.666666666666657</v>
+      </c>
+      <c r="C12">
+        <v>0.43615005683971197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>82.5</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.4520547945205479</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="C13">
+        <v>0.45205479452054792</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
-        <v>85.16666666666667</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.4813066410233995</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="B14">
+        <v>85.166666666666671</v>
+      </c>
+      <c r="C14">
+        <v>0.48130664102339948</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>67.5</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.4029850746268657</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="C15">
+        <v>0.40298507462686572</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
-        <v>55.33333333333334</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.5091575091575091</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="B16">
+        <v>55.333333333333343</v>
+      </c>
+      <c r="C16">
+        <v>0.50915750915750912</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
-        <v>57.33333333333334</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.5635123614663257</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="B17">
+        <v>57.333333333333343</v>
+      </c>
+      <c r="C17">
+        <v>0.56351236146632566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6115549455529515</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="B18">
+        <v>66.666666666666657</v>
+      </c>
+      <c r="C18">
+        <v>0.61155494555295153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>62.5</v>
       </c>
-      <c r="C19" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="C19">
+        <v>0.38461538461538458</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>67.5</v>
       </c>
-      <c r="C20" t="n">
-        <v>0.4078677672566058</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="C20">
+        <v>0.40786776725660578</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
-        <v>77.83333333333333</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.5018446729216998</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="B21">
+        <v>77.833333333333329</v>
+      </c>
+      <c r="C21">
+        <v>0.50184467292169976</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
-        <v>80.33333333333333</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.4693608346324499</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="B22">
+        <v>80.333333333333329</v>
+      </c>
+      <c r="C22">
+        <v>0.46936083463244987</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>62.5</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.597436715560711</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="C23">
+        <v>0.59743671556071098</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
-        <v>54.83333333333334</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.5311080671905415</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="B24">
+        <v>54.833333333333343</v>
+      </c>
+      <c r="C24">
+        <v>0.53110806719054149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>82.5</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.4520547945205479</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="C25">
+        <v>0.45205479452054792</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
-        <v>72.83333333333334</v>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26">
+        <v>72.833333333333343</v>
+      </c>
+      <c r="C26">
         <v>0.4387020127525984</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
-        <v>56.66666666666666</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.3754403945935558</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="B27">
+        <v>56.666666666666657</v>
+      </c>
+      <c r="C27">
+        <v>0.37544039459355583</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>68</v>
       </c>
-      <c r="C28" t="n">
-        <v>0.4193431319179822</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="C28">
+        <v>0.41934313191798223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
-        <v>55.33333333333334</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.3726493859142621</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="B29">
+        <v>55.333333333333343</v>
+      </c>
+      <c r="C29">
+        <v>0.37264938591426211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
-        <v>63.66666666666667</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.5526675786593708</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="B30">
+        <v>63.666666666666671</v>
+      </c>
+      <c r="C30">
+        <v>0.55266757865937077</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
-        <v>50.33333333333333</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.4492632201468632</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="B31">
+        <v>50.333333333333329</v>
+      </c>
+      <c r="C31">
+        <v>0.44926322014686321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
-        <v>52.33333333333333</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.4878162346732888</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="B32">
+        <v>52.333333333333329</v>
+      </c>
+      <c r="C32">
+        <v>0.48781623467328877</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
-        <v>67.66666666666666</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.418</v>
+      <c r="B33">
+        <v>67.666666666666657</v>
+      </c>
+      <c r="C33">
+        <v>0.41799999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>7.15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>